--- a/public/attachments/Obligation Request.xlsx
+++ b/public/attachments/Obligation Request.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernesto/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernesto/Documents/Capstone Projects/Payroll System/public/attachments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F188962-DDD7-6D46-A1CC-09000E99115A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{426AA877-0E56-654F-96C4-7D53D29A94AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" xr2:uid="{5B013A8F-4F72-A847-A040-D46798FFFDE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -495,6 +496,45 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -516,33 +556,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -554,18 +567,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -890,250 +891,250 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="49" t="s">
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="49"/>
+      <c r="G4" s="53"/>
     </row>
     <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="50" t="s">
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="50"/>
+      <c r="G5" s="54"/>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
     </row>
     <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="37" t="s">
+      <c r="C9" s="47"/>
+      <c r="D9" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="47"/>
-      <c r="G9" s="37" t="s">
+      <c r="F9" s="44"/>
+      <c r="G9" s="50" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="38"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="38"/>
+      <c r="G10" s="51"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="54">
+      <c r="C11" s="33"/>
+      <c r="D11" s="34">
         <v>1011</v>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="34">
         <v>706</v>
       </c>
-      <c r="F11" s="54" t="s">
+      <c r="F11" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="40"/>
+      <c r="G11" s="37"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="20"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="41"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="38"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="20"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="41"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="38"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="20"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="41"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="38"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="20"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="41"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="38"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="20"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="41"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="38"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="20"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="41"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="38"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="20"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="41"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="38"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="20"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="41"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="38"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="20"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="41"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="38"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="20"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="41"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="38"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="42"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="39"/>
     </row>
     <row r="23" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
@@ -1358,17 +1359,17 @@
     <mergeCell ref="B9:C10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="G9:G10"/>
-    <mergeCell ref="B11:C22"/>
-    <mergeCell ref="D11:D22"/>
-    <mergeCell ref="E11:E22"/>
-    <mergeCell ref="F11:F22"/>
-    <mergeCell ref="G11:G22"/>
     <mergeCell ref="A11:A22"/>
     <mergeCell ref="A25:C29"/>
     <mergeCell ref="D25:G29"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B11:C22"/>
+    <mergeCell ref="D11:D22"/>
+    <mergeCell ref="E11:E22"/>
+    <mergeCell ref="F11:F22"/>
+    <mergeCell ref="G11:G22"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="E31:G31"/>
     <mergeCell ref="E30:G30"/>
